--- a/resources/digital-products/files/dp-inter-tier-bump.xlsx
+++ b/resources/digital-products/files/dp-inter-tier-bump.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="11">
@@ -526,7 +526,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -572,7 +572,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Entry price (£)</t>
+          <t>Entry price ($)</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
@@ -582,7 +582,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Order-bump price (£)</t>
+          <t>Order-bump price ($)</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -640,7 +640,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Revenue in the period (£)</t>
+          <t>Revenue in the period ($)</t>
         </is>
       </c>
       <c r="B13" s="11">
@@ -651,7 +651,7 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Average order value (£)</t>
+          <t>Average order value ($)</t>
         </is>
       </c>
       <c r="B14" s="11">
@@ -667,7 +667,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Book: £19 entry, £39 bump, 20 orders, 25% take → £575 revenue, £28.75 average order.</t>
+          <t>Book: $19 entry, $39 bump, 20 orders, 25% take → $575 revenue, $28.75 average order.</t>
         </is>
       </c>
     </row>
@@ -695,5 +695,6 @@
     <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/resources/digital-products/files/dp-inter-tier-bump.xlsx
+++ b/resources/digital-products/files/dp-inter-tier-bump.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -614,6 +615,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -664,6 +666,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -671,6 +674,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="12" t="n"/>
@@ -683,12 +687,17 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
